--- a/site/exports/dlut-architecture-art.xlsx
+++ b/site/exports/dlut-architecture-art.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47.59999999999999" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>建筑与艺术学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Purposeful sample only, not original-order, ranked or full-coverage.；Current personnel and mentor employment unknown; navigation false.；No exact degree conferral dates/years inferred; unconfirmed degree awards remain null.；Only necessary professional excerpts retained, not original HTML or whole pages.；Two official-site bibliographic samples only; publisher metadata unverified; no paper full texts read.；Francois Chaslin relation is unspecified French-study mentorship, not a doctoral-advisor fact. DPLG not equated with a master's award.；来源差异/限制：巴黎先贤祠索邦大学；法国第一大学（巴黎先贤祠-索邦大学）；Same source uses these variants; no external institutional/legal normalization.；来源差异/限制：header_title：基于场所精神的滨海特色商业街改造设计研究——以旅顺塔河湾海鲜街为例；body_title：中法住宅遗产认定与住区保护机制的比较观察：对话建筑遗产研究者；Retain conflicting header separately. Selected work metadata follows body heading plus matching native list; no silent title substitution or third work accepted.；来源记载职业信息：职业资格标签：副教授；博士生导师；硕士生导师。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16.8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -601,9 +655,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="51.8" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="47.59999999999999" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1030,14 +1084,726 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>巴黎先贤祠索邦大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2005-12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>地理学城市规划</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Profile explicitly states doctoral graduation/holding; no award date inferred. Narrative 法国第一大学（巴黎先贤祠-索邦大学） preserved as the source's naming variant.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；本轮另据官方页面明确资格文字保留博士学位自述；不推定授位日期、导师或当前任职，非证书认证。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>里尔建筑与景观学校</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2003-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2006-04</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>建筑学</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Education-row label only. The separate DPLG credential is not silently equated with a master's award.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1998-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2001-03</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>建筑学</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Education-row label only; no explicit conferral statement.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1993-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1998-07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>建筑学</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Education-row label only; no explicit conferral statement.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（end_source_label）：至今</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>建筑师</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Nasrine Seraji 建筑与规划事务所</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2006-11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2007-11</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>建筑师</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Du Besset &amp; Lyon 建筑事务所</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2006-09</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2006-10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>建筑师</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Leonard &amp; Weissmann 建筑事务所</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2006-06</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2006-07</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>建筑师</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Odile Decq 建筑事务所</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2005-02</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2005-06</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>建筑师</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Olivier Chaslin建筑事务所</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2005-01</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>教师</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2001-04</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2003-08</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1049,18 +1815,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22.4" customWidth="1" min="2" max="2"/>
+    <col width="39.2" customWidth="1" min="3" max="3"/>
+    <col width="37.8" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1128,8 +1894,61 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Francois Chaslin</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>study_mentorship_unspecified</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>study_in_france_unspecified</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。；来源指导关系语境：mentor_profession：建筑评论家；mentor_country_description：法国；learner_context：在法国留学期间；具体机构、日期及学位阶段未知。保留原语境，不据此新认定学位阶段、导师身份或当前任职。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1140,19 +1959,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1219,8 +2038,118 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>基于USGS卫星图的庄河上下街历史地段院落形态识别与解析</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_listed：李冰；来源书目信息（volume_source_label）：43；来源书目信息（期）：08；来源书目信息（页码）：11-15；来源书目信息（publication_date_source）：2025-08-10</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中法住宅遗产认定与住区保护机制的比较观察：对话建筑遗产研究者</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_listed：李冰、朱文健；来源书目信息（volume_source_label）：40；来源书目信息（期）：03；来源书目信息（页码）：53-57；来源书目信息（publication_date_source）：2025-06-10</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1231,14 +2160,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="47.59999999999999" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="58.8" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1313,10 +2242,238 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s001-40732b8e811f</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:33.973Z</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s002-cf9bf47cadba</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://aaschool.dlut.edu.cn/szdw/jsml.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:39.823Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s003-2572fbb8eb69</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:45.873Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s004-6a799dffc154</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/lwcg/674738/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:45.873Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s005-7a9933e3d440</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/lwcg/674738/content/351389.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:04:36.036Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>李冰</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-libing-s006-1b323f85fa77</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/libing_architecture/zh_CN/lwcg/674738/content/351388.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:04:40.098Z</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/dlut-architecture-art.xlsx
+++ b/site/exports/dlut-architecture-art.xlsx
@@ -1265,7 +1265,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
